--- a/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezmat_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_indicadores/plot_regional_grupos_e_rezmat_a_2022_nuble.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 03:59</t>
+    <t xml:space="preserve">2026-10-05 06:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
